--- a/Ambiente Productivo/Lift-and-Shift - 18 Servers/analysis_TCO.xlsx
+++ b/Ambiente Productivo/Lift-and-Shift - 18 Servers/analysis_TCO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\C29652e\projects\Assessment\Assessment\Ambiente Productivo\Lift-and-Shift - 18 Servers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{158F2D30-E1FD-4146-A1BD-5FB78D0BB8F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{640EC051-7138-40DA-BDB3-7171491C3AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,11 @@
     <sheet name="Glossary" sheetId="2" r:id="rId2"/>
     <sheet name="Shared Tenancy Analysis" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Shared Tenancy Analysis'!$A$1:$AB$24</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="127">
   <si>
     <t>Host Name Onpremise</t>
   </si>
@@ -145,10 +149,6 @@
     <t>PAHWPAPSRC03</t>
   </si>
   <si>
-    <t>USAEA1PWBWES23 
-USAEA1PWBWES24</t>
-  </si>
-  <si>
     <t>Windows</t>
   </si>
   <si>
@@ -158,10 +158,6 @@
     <t>PAHWPAPWFC01</t>
   </si>
   <si>
-    <t>USAEA1PWBWES25 
-USAEA1PWBWES26</t>
-  </si>
-  <si>
     <t>r7a.medium</t>
   </si>
   <si>
@@ -174,16 +170,9 @@
     <t>PAHWPWSAPI01</t>
   </si>
   <si>
-    <t>USAEA1PWBWES35</t>
-  </si>
-  <si>
     <t>PAHWPAPWSS03</t>
   </si>
   <si>
-    <t>USAEA1PWBWES27 
-USAEA1PWBWES28</t>
-  </si>
-  <si>
     <t>PAHWPAPWEF02</t>
   </si>
   <si>
@@ -193,10 +182,6 @@
     <t>PAHWPAPTUI03</t>
   </si>
   <si>
-    <t>USAEA1PWBWES21 
-USAEA1PWBWES22</t>
-  </si>
-  <si>
     <t>Microsoft Windows Server 2025 (64-bit) [ASG app1 desplegado]</t>
   </si>
   <si>
@@ -209,9 +194,6 @@
     <t>pahqpapapp02</t>
   </si>
   <si>
-    <t>USAEA1PAPWES33</t>
-  </si>
-  <si>
     <t>Windows Server 2025 Standard</t>
   </si>
   <si>
@@ -414,6 +396,30 @@
   </si>
   <si>
     <t>Compute-only yearly cost with 3-year RI</t>
+  </si>
+  <si>
+    <t>USAEA1PWBWESPA1-5</t>
+  </si>
+  <si>
+    <t>USAEA1PWBWESPB1-5</t>
+  </si>
+  <si>
+    <t>USAEA1PWBWESPC1-5</t>
+  </si>
+  <si>
+    <t>USAEA1PWBWESPD1-5</t>
+  </si>
+  <si>
+    <t>USAEA1PWBWESPE1-5</t>
+  </si>
+  <si>
+    <t>USAEA1PWBWESPF1-5</t>
+  </si>
+  <si>
+    <t>USAEA1PWBWESPG1-5</t>
+  </si>
+  <si>
+    <t>PAHWPFSASC01</t>
   </si>
 </sst>
 </file>
@@ -445,7 +451,7 @@
       <name val="Amazon Ember"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -468,6 +474,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor theme="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -505,7 +523,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1"/>
@@ -523,6 +541,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -746,31 +769,31 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -1769,15 +1792,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1785,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1793,15 +1816,15 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1809,7 +1832,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1817,7 +1840,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1825,7 +1848,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1833,7 +1856,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1841,7 +1864,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1849,7 +1872,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1857,7 +1880,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1865,7 +1888,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1873,15 +1896,15 @@
         <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1889,7 +1912,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1897,7 +1920,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1905,7 +1928,7 @@
         <v>19</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1913,7 +1936,7 @@
         <v>20</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1921,7 +1944,7 @@
         <v>21</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15.75" customHeight="1">
@@ -1929,7 +1952,7 @@
         <v>23</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="15.75" customHeight="1">
@@ -1937,7 +1960,7 @@
         <v>24</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15.75" customHeight="1">
@@ -1945,7 +1968,7 @@
         <v>26</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="15.75" customHeight="1">
@@ -1953,7 +1976,7 @@
         <v>27</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="15.75" customHeight="1"/>
@@ -2940,7 +2963,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AB999"/>
+  <dimension ref="A1:AC1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="51.5703125" bestFit="1" customWidth="1"/>
@@ -3060,167 +3083,167 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="15.75" customHeight="1">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:28" s="13" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A2" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6" t="s">
+      <c r="B2" s="11"/>
+      <c r="C2" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="11">
         <v>4</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="11">
         <v>16</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="11">
         <v>2</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="11">
         <v>16</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="11">
         <v>520</v>
       </c>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6" t="s">
+      <c r="M2" s="11"/>
+      <c r="N2" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="6">
+      <c r="O2" s="11">
         <v>41.6</v>
       </c>
-      <c r="P2" s="6">
-        <f t="shared" ref="P2:P15" si="0">PRODUCT(O2,12)</f>
+      <c r="P2" s="11">
+        <f t="shared" ref="P2:P16" si="0">PRODUCT(O2,12)</f>
         <v>499.20000000000005</v>
       </c>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6">
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11">
         <v>104</v>
       </c>
-      <c r="T2" s="6">
-        <f t="shared" ref="T2:T23" si="1">PRODUCT(S2,12)</f>
+      <c r="T2" s="11">
+        <f t="shared" ref="T2:T24" si="1">PRODUCT(S2,12)</f>
         <v>1248</v>
       </c>
-      <c r="U2" s="6">
+      <c r="U2" s="11">
         <v>0</v>
       </c>
-      <c r="V2" s="6">
+      <c r="V2" s="11">
         <v>1244</v>
       </c>
-      <c r="W2" s="6">
+      <c r="W2" s="11">
         <v>73</v>
       </c>
-      <c r="X2" s="6">
-        <f t="shared" ref="X2:X15" si="2">PRODUCT(W2,12)</f>
+      <c r="X2" s="11">
+        <f t="shared" ref="X2:X16" si="2">PRODUCT(W2,12)</f>
         <v>876</v>
       </c>
-      <c r="Y2" s="6">
+      <c r="Y2" s="11">
         <v>876</v>
       </c>
-      <c r="Z2" s="6">
+      <c r="Z2" s="11">
         <v>57</v>
       </c>
-      <c r="AA2" s="6">
-        <f t="shared" ref="AA2:AA13" si="3">PRODUCT(Z2,12)</f>
+      <c r="AA2" s="11">
+        <f t="shared" ref="AA2:AA14" si="3">PRODUCT(Z2,12)</f>
         <v>684</v>
       </c>
-      <c r="AB2" s="2">
+      <c r="AB2" s="12">
         <v>683</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="15.75" customHeight="1">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:28" s="13" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A3" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="11"/>
+      <c r="C3" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="11">
         <v>4</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="11">
         <v>16</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="11">
         <v>2</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="11">
         <v>16</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="11">
         <v>210</v>
       </c>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6" t="s">
+      <c r="M3" s="11"/>
+      <c r="N3" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="O3" s="6">
+      <c r="O3" s="11">
         <v>16.8</v>
       </c>
-      <c r="P3" s="6">
+      <c r="P3" s="11">
         <f t="shared" si="0"/>
         <v>201.60000000000002</v>
       </c>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6">
+      <c r="Q3" s="11"/>
+      <c r="R3" s="11"/>
+      <c r="S3" s="11">
         <v>104</v>
       </c>
-      <c r="T3" s="6">
+      <c r="T3" s="11">
         <f t="shared" si="1"/>
         <v>1248</v>
       </c>
-      <c r="U3" s="6">
+      <c r="U3" s="11">
         <v>0</v>
       </c>
-      <c r="V3" s="6">
+      <c r="V3" s="11">
         <v>1244</v>
       </c>
-      <c r="W3" s="6">
+      <c r="W3" s="11">
         <v>73</v>
       </c>
-      <c r="X3" s="6">
+      <c r="X3" s="11">
         <f t="shared" si="2"/>
         <v>876</v>
       </c>
-      <c r="Y3" s="6">
+      <c r="Y3" s="11">
         <v>876</v>
       </c>
-      <c r="Z3" s="6">
+      <c r="Z3" s="11">
         <v>57</v>
       </c>
-      <c r="AA3" s="6">
+      <c r="AA3" s="11">
         <f t="shared" si="3"/>
         <v>684</v>
       </c>
-      <c r="AB3" s="2">
+      <c r="AB3" s="12">
         <v>683</v>
       </c>
     </row>
@@ -3229,7 +3252,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>29</v>
@@ -3241,10 +3264,10 @@
         <v>16</v>
       </c>
       <c r="F4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>32</v>
@@ -3310,10 +3333,10 @@
     </row>
     <row r="5" spans="1:28" ht="30" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>40</v>
+        <v>121</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>29</v>
@@ -3325,16 +3348,16 @@
         <v>8</v>
       </c>
       <c r="F5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="9" t="s">
-        <v>38</v>
-      </c>
       <c r="H5" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J5" s="9">
         <v>1</v>
@@ -3394,10 +3417,10 @@
     </row>
     <row r="6" spans="1:28" ht="15.75" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>29</v>
@@ -3409,16 +3432,16 @@
         <v>8</v>
       </c>
       <c r="F6" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="G6" s="6" t="s">
-        <v>38</v>
-      </c>
       <c r="H6" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J6" s="6">
         <v>1</v>
@@ -3485,10 +3508,10 @@
     </row>
     <row r="7" spans="1:28" ht="15.75" customHeight="1">
       <c r="A7" s="9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>29</v>
@@ -3500,10 +3523,10 @@
         <v>16</v>
       </c>
       <c r="F7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="9" t="s">
         <v>37</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>38</v>
       </c>
       <c r="H7" s="9" t="s">
         <v>32</v>
@@ -3575,10 +3598,10 @@
     </row>
     <row r="8" spans="1:28" ht="30" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>47</v>
+        <v>122</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>29</v>
@@ -3590,16 +3613,16 @@
         <v>8</v>
       </c>
       <c r="F8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="9" t="s">
-        <v>38</v>
-      </c>
       <c r="H8" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J8" s="9">
         <v>1</v>
@@ -3659,10 +3682,10 @@
     </row>
     <row r="9" spans="1:28" ht="15.75" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>29</v>
@@ -3674,16 +3697,16 @@
         <v>8</v>
       </c>
       <c r="F9" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="G9" s="9" t="s">
-        <v>38</v>
-      </c>
       <c r="H9" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J9" s="9">
         <v>1</v>
@@ -3749,10 +3772,10 @@
     </row>
     <row r="10" spans="1:28" ht="30.75" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>29</v>
@@ -3764,16 +3787,16 @@
         <v>8</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J10" s="9">
         <v>1</v>
@@ -3833,10 +3856,10 @@
     </row>
     <row r="11" spans="1:28" ht="30" customHeight="1">
       <c r="A11" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>29</v>
@@ -3848,10 +3871,10 @@
         <v>16</v>
       </c>
       <c r="F11" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="9" t="s">
         <v>37</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>38</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>32</v>
@@ -3923,10 +3946,10 @@
     </row>
     <row r="12" spans="1:28" ht="15.75" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>56</v>
+        <v>125</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>29</v>
@@ -3938,16 +3961,16 @@
         <v>8</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J12" s="9">
         <v>4</v>
@@ -4005,335 +4028,306 @@
         <v>302.31</v>
       </c>
     </row>
-    <row r="13" spans="1:28" ht="15.75" customHeight="1">
+    <row r="13" spans="1:28" s="15" customFormat="1" ht="15.75" customHeight="1">
       <c r="A13" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9"/>
+      <c r="S13" s="9"/>
+      <c r="T13" s="9"/>
+      <c r="U13" s="9"/>
+      <c r="V13" s="9"/>
+      <c r="W13" s="9"/>
+      <c r="X13" s="9"/>
+      <c r="Y13" s="9"/>
+      <c r="Z13" s="9"/>
+      <c r="AA13" s="9"/>
+      <c r="AB13" s="2"/>
+    </row>
+    <row r="14" spans="1:28" s="13" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A14" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D14" s="14">
         <v>4</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E14" s="14">
         <v>2</v>
       </c>
-      <c r="F13" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="J13" s="9">
+      <c r="F14" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="H14" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="J14" s="14">
         <v>2</v>
       </c>
-      <c r="K13" s="9">
+      <c r="K14" s="14">
         <v>4</v>
       </c>
-      <c r="L13" s="9">
+      <c r="L14" s="14">
         <v>210</v>
       </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9" t="s">
+      <c r="M14" s="14"/>
+      <c r="N14" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="O13" s="9">
+      <c r="O14" s="14">
         <v>16.8</v>
       </c>
-      <c r="P13" s="9">
+      <c r="P14" s="14">
         <f t="shared" si="0"/>
         <v>201.60000000000002</v>
       </c>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="9"/>
-      <c r="S13" s="9">
+      <c r="Q14" s="14"/>
+      <c r="R14" s="14"/>
+      <c r="S14" s="14">
         <v>56.21</v>
       </c>
-      <c r="T13" s="9">
+      <c r="T14" s="14">
         <f t="shared" si="1"/>
         <v>674.52</v>
       </c>
-      <c r="U13" s="9">
+      <c r="U14" s="14">
         <v>0</v>
       </c>
-      <c r="V13" s="9">
+      <c r="V14" s="14">
         <v>674.52</v>
       </c>
-      <c r="W13" s="9">
+      <c r="W14" s="14">
         <v>35.770000000000003</v>
       </c>
-      <c r="X13" s="9">
+      <c r="X14" s="14">
         <f t="shared" si="2"/>
         <v>429.24</v>
       </c>
-      <c r="Y13" s="9">
+      <c r="Y14" s="14">
         <v>429.24</v>
       </c>
-      <c r="Z13" s="9">
+      <c r="Z14" s="14">
         <v>24.09</v>
       </c>
-      <c r="AA13" s="9">
+      <c r="AA14" s="14">
         <f t="shared" si="3"/>
         <v>289.08</v>
       </c>
-      <c r="AB13" s="2">
+      <c r="AB14" s="12">
         <v>289.08</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28" ht="15.75" customHeight="1">
-      <c r="A14" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="9">
-        <v>16</v>
-      </c>
-      <c r="E14" s="9">
-        <v>128</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="J14" s="9">
-        <v>16</v>
-      </c>
-      <c r="K14" s="9">
-        <v>128</v>
-      </c>
-      <c r="L14" s="9">
-        <v>1700</v>
-      </c>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="O14" s="9">
-        <v>391</v>
-      </c>
-      <c r="P14" s="9">
-        <f t="shared" si="0"/>
-        <v>4692</v>
-      </c>
-      <c r="Q14" s="9"/>
-      <c r="R14" s="9"/>
-      <c r="S14" s="9">
-        <v>8876.7999999999993</v>
-      </c>
-      <c r="T14" s="9">
-        <f t="shared" si="1"/>
-        <v>106521.59999999999</v>
-      </c>
-      <c r="U14" s="9">
-        <v>54382.080000000002</v>
-      </c>
-      <c r="V14" s="9">
-        <v>52139.519999999997</v>
-      </c>
-      <c r="W14" s="9">
-        <v>8388.58</v>
-      </c>
-      <c r="X14" s="9">
-        <f t="shared" si="2"/>
-        <v>100662.95999999999</v>
-      </c>
-      <c r="Y14" s="9"/>
-      <c r="Z14" s="9">
-        <f>AA14/12</f>
-        <v>20878.25</v>
-      </c>
-      <c r="AA14" s="9">
-        <v>250539</v>
-      </c>
-      <c r="AB14" s="2" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:28" ht="15.75" customHeight="1">
       <c r="A15" s="9" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B15" s="9"/>
       <c r="C15" s="9" t="s">
         <v>29</v>
       </c>
       <c r="D15" s="9">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E15" s="9">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="J15" s="9">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K15" s="9">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="L15" s="9">
-        <v>2900</v>
+        <v>1700</v>
       </c>
       <c r="M15" s="9"/>
       <c r="N15" s="9" t="s">
         <v>33</v>
       </c>
       <c r="O15" s="9">
-        <v>333.5</v>
+        <v>391</v>
       </c>
       <c r="P15" s="9">
         <f t="shared" si="0"/>
-        <v>4002</v>
+        <v>4692</v>
       </c>
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
       <c r="S15" s="9">
-        <v>2219.1999999999998</v>
+        <v>8876.7999999999993</v>
       </c>
       <c r="T15" s="9">
         <f t="shared" si="1"/>
-        <v>26630.399999999998</v>
+        <v>106521.59999999999</v>
       </c>
       <c r="U15" s="9">
-        <v>13595.52</v>
+        <v>54382.080000000002</v>
       </c>
       <c r="V15" s="9">
-        <v>13034.88</v>
+        <v>52139.519999999997</v>
       </c>
       <c r="W15" s="9">
-        <v>2097.14</v>
+        <v>8388.58</v>
       </c>
       <c r="X15" s="9">
         <f t="shared" si="2"/>
-        <v>25165.68</v>
+        <v>100662.95999999999</v>
       </c>
       <c r="Y15" s="9"/>
       <c r="Z15" s="9">
         <f>AA15/12</f>
-        <v>5219.583333333333</v>
+        <v>20878.25</v>
       </c>
       <c r="AA15" s="9">
-        <v>62635</v>
+        <v>250539</v>
       </c>
       <c r="AB15" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:28" ht="15.75" customHeight="1">
-      <c r="A16" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6" t="s">
+      <c r="A16" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6">
-        <v>100</v>
-      </c>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6" t="s">
+      <c r="D16" s="9">
+        <v>8</v>
+      </c>
+      <c r="E16" s="9">
+        <v>64</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="J16" s="9">
+        <v>8</v>
+      </c>
+      <c r="K16" s="9">
+        <v>64</v>
+      </c>
+      <c r="L16" s="9">
+        <v>2900</v>
+      </c>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="6"/>
-      <c r="R16" s="6"/>
-      <c r="S16" s="6">
-        <v>147.30000000000001</v>
-      </c>
-      <c r="T16" s="6">
+      <c r="O16" s="9">
+        <v>333.5</v>
+      </c>
+      <c r="P16" s="9">
+        <f t="shared" si="0"/>
+        <v>4002</v>
+      </c>
+      <c r="Q16" s="9"/>
+      <c r="R16" s="9"/>
+      <c r="S16" s="9">
+        <v>2219.1999999999998</v>
+      </c>
+      <c r="T16" s="9">
         <f t="shared" si="1"/>
-        <v>1767.6000000000001</v>
-      </c>
-      <c r="U16" s="6">
-        <v>0</v>
-      </c>
-      <c r="V16" s="6">
-        <v>1689.6</v>
-      </c>
-      <c r="W16" s="6"/>
-      <c r="X16" s="6"/>
-      <c r="Y16" s="6"/>
-      <c r="Z16" s="6"/>
-      <c r="AA16" s="6"/>
-      <c r="AB16" s="2"/>
+        <v>26630.399999999998</v>
+      </c>
+      <c r="U16" s="9">
+        <v>13595.52</v>
+      </c>
+      <c r="V16" s="9">
+        <v>13034.88</v>
+      </c>
+      <c r="W16" s="9">
+        <v>2097.14</v>
+      </c>
+      <c r="X16" s="9">
+        <f t="shared" si="2"/>
+        <v>25165.68</v>
+      </c>
+      <c r="Y16" s="9"/>
+      <c r="Z16" s="9">
+        <f>AA16/12</f>
+        <v>5219.583333333333</v>
+      </c>
+      <c r="AA16" s="9">
+        <v>62635</v>
+      </c>
+      <c r="AB16" s="2" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="17" spans="1:28" ht="15.75" customHeight="1">
       <c r="A17" s="7" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="6">
-        <v>2</v>
-      </c>
-      <c r="E17" s="6">
-        <v>8</v>
-      </c>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
       <c r="F17" s="6" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="J17" s="6">
-        <v>2</v>
-      </c>
-      <c r="K17" s="6">
-        <v>8</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
       <c r="L17" s="6">
         <v>100</v>
       </c>
@@ -4341,169 +4335,183 @@
       <c r="N17" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="O17" s="6">
-        <v>8</v>
-      </c>
-      <c r="P17" s="6">
-        <f>PRODUCT(O17,12)</f>
-        <v>96</v>
-      </c>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6"/>
       <c r="Q17" s="6"/>
       <c r="R17" s="6"/>
       <c r="S17" s="6">
-        <v>137.24</v>
+        <v>147.30000000000001</v>
       </c>
       <c r="T17" s="6">
         <f t="shared" si="1"/>
-        <v>1646.88</v>
+        <v>1767.6000000000001</v>
       </c>
       <c r="U17" s="6">
-        <v>805.92</v>
+        <v>0</v>
       </c>
       <c r="V17" s="6">
-        <v>840.96</v>
-      </c>
-      <c r="W17" s="6">
-        <v>110.96</v>
-      </c>
-      <c r="X17" s="6">
-        <f>PRODUCT(W17,12)</f>
-        <v>1331.52</v>
-      </c>
-      <c r="Y17" s="6">
-        <v>525.6</v>
-      </c>
-      <c r="Z17" s="6">
-        <v>97.09</v>
-      </c>
-      <c r="AA17" s="6">
-        <f>PRODUCT(Z17,12)</f>
-        <v>1165.08</v>
-      </c>
-      <c r="AB17" s="2">
-        <v>359.16</v>
-      </c>
+        <v>1689.6</v>
+      </c>
+      <c r="W17" s="6"/>
+      <c r="X17" s="6"/>
+      <c r="Y17" s="6"/>
+      <c r="Z17" s="6"/>
+      <c r="AA17" s="6"/>
+      <c r="AB17" s="2"/>
     </row>
     <row r="18" spans="1:28" ht="15.75" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D18" s="6">
+        <v>2</v>
+      </c>
+      <c r="E18" s="6">
         <v>8</v>
       </c>
-      <c r="E18" s="6">
-        <v>16</v>
-      </c>
       <c r="F18" s="6" t="s">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="J18" s="6">
+        <v>2</v>
+      </c>
+      <c r="K18" s="6">
         <v>8</v>
       </c>
-      <c r="K18" s="6">
-        <v>16</v>
-      </c>
       <c r="L18" s="6">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M18" s="6"/>
       <c r="N18" s="6" t="s">
         <v>33</v>
       </c>
       <c r="O18" s="6">
-        <v>5.75</v>
+        <v>8</v>
       </c>
       <c r="P18" s="6">
         <f>PRODUCT(O18,12)</f>
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="Q18" s="6"/>
       <c r="R18" s="6"/>
       <c r="S18" s="6">
-        <v>347.48</v>
+        <v>137.24</v>
       </c>
       <c r="T18" s="6">
         <f t="shared" si="1"/>
-        <v>4169.76</v>
+        <v>1646.88</v>
       </c>
       <c r="U18" s="6">
-        <v>0</v>
+        <v>805.92</v>
       </c>
       <c r="V18" s="6">
-        <v>4169.76</v>
-      </c>
-      <c r="W18" s="6"/>
-      <c r="X18" s="6"/>
-      <c r="Y18" s="6"/>
-      <c r="Z18" s="6"/>
-      <c r="AA18" s="6"/>
-      <c r="AB18" s="2"/>
+        <v>840.96</v>
+      </c>
+      <c r="W18" s="6">
+        <v>110.96</v>
+      </c>
+      <c r="X18" s="6">
+        <f>PRODUCT(W18,12)</f>
+        <v>1331.52</v>
+      </c>
+      <c r="Y18" s="6">
+        <v>525.6</v>
+      </c>
+      <c r="Z18" s="6">
+        <v>97.09</v>
+      </c>
+      <c r="AA18" s="6">
+        <f>PRODUCT(Z18,12)</f>
+        <v>1165.08</v>
+      </c>
+      <c r="AB18" s="2">
+        <v>359.16</v>
+      </c>
     </row>
-    <row r="19" spans="1:28" ht="15.75">
+    <row r="19" spans="1:28" ht="15.75" customHeight="1">
       <c r="A19" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7" t="s">
+      <c r="D19" s="6">
+        <v>8</v>
+      </c>
+      <c r="E19" s="6">
+        <v>16</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J19" s="6">
+        <v>8</v>
+      </c>
+      <c r="K19" s="6">
+        <v>16</v>
+      </c>
+      <c r="L19" s="6">
+        <v>50</v>
+      </c>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="O19" s="7"/>
-      <c r="P19" s="7"/>
-      <c r="Q19" s="7"/>
-      <c r="R19" s="7"/>
-      <c r="S19" s="7">
-        <v>39.78</v>
+      <c r="O19" s="6">
+        <v>5.75</v>
+      </c>
+      <c r="P19" s="6">
+        <f>PRODUCT(O19,12)</f>
+        <v>69</v>
+      </c>
+      <c r="Q19" s="6"/>
+      <c r="R19" s="6"/>
+      <c r="S19" s="6">
+        <v>347.48</v>
       </c>
       <c r="T19" s="6">
         <f t="shared" si="1"/>
-        <v>477.36</v>
-      </c>
-      <c r="U19" s="7"/>
-      <c r="V19" s="7"/>
-      <c r="W19" s="7"/>
-      <c r="X19" s="7"/>
-      <c r="Y19" s="7"/>
-      <c r="Z19" s="7"/>
-      <c r="AA19" s="7"/>
+        <v>4169.76</v>
+      </c>
+      <c r="U19" s="6">
+        <v>0</v>
+      </c>
+      <c r="V19" s="6">
+        <v>4169.76</v>
+      </c>
+      <c r="W19" s="6"/>
+      <c r="X19" s="6"/>
+      <c r="Y19" s="6"/>
+      <c r="Z19" s="6"/>
+      <c r="AA19" s="6"/>
       <c r="AB19" s="2"/>
     </row>
-    <row r="20" spans="1:28" ht="15.75" customHeight="1">
+    <row r="20" spans="1:28" ht="15.75">
       <c r="A20" s="7" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7" t="s">
@@ -4512,16 +4520,16 @@
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -4535,11 +4543,11 @@
       <c r="Q20" s="7"/>
       <c r="R20" s="7"/>
       <c r="S20" s="7">
-        <v>0.09</v>
+        <v>39.78</v>
       </c>
       <c r="T20" s="6">
         <f t="shared" si="1"/>
-        <v>1.08</v>
+        <v>477.36</v>
       </c>
       <c r="U20" s="7"/>
       <c r="V20" s="7"/>
@@ -4552,7 +4560,7 @@
     </row>
     <row r="21" spans="1:28" ht="15.75" customHeight="1">
       <c r="A21" s="7" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7" t="s">
@@ -4561,16 +4569,16 @@
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -4584,11 +4592,11 @@
       <c r="Q21" s="7"/>
       <c r="R21" s="7"/>
       <c r="S21" s="7">
-        <v>1.1499999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="T21" s="6">
         <f t="shared" si="1"/>
-        <v>13.799999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="U21" s="7"/>
       <c r="V21" s="7"/>
@@ -4601,7 +4609,7 @@
     </row>
     <row r="22" spans="1:28" ht="15.75" customHeight="1">
       <c r="A22" s="7" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7" t="s">
@@ -4610,16 +4618,16 @@
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G22" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="G22" s="7" t="s">
-        <v>90</v>
-      </c>
       <c r="H22" s="7" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -4633,11 +4641,11 @@
       <c r="Q22" s="7"/>
       <c r="R22" s="7"/>
       <c r="S22" s="7">
-        <v>2</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="T22" s="6">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>13.799999999999999</v>
       </c>
       <c r="U22" s="7"/>
       <c r="V22" s="7"/>
@@ -4650,7 +4658,7 @@
     </row>
     <row r="23" spans="1:28" ht="15.75" customHeight="1">
       <c r="A23" s="7" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7" t="s">
@@ -4659,16 +4667,16 @@
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
@@ -4682,11 +4690,11 @@
       <c r="Q23" s="7"/>
       <c r="R23" s="7"/>
       <c r="S23" s="7">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="T23" s="6">
         <f t="shared" si="1"/>
-        <v>9.6000000000000014</v>
+        <v>24</v>
       </c>
       <c r="U23" s="7"/>
       <c r="V23" s="7"/>
@@ -4697,7 +4705,55 @@
       <c r="AA23" s="7"/>
       <c r="AB23" s="2"/>
     </row>
-    <row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <row r="24" spans="1:28" ht="15.75" customHeight="1">
+      <c r="A24" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O24" s="7"/>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7"/>
+      <c r="R24" s="7"/>
+      <c r="S24" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="T24" s="6">
+        <f t="shared" si="1"/>
+        <v>9.6000000000000014</v>
+      </c>
+      <c r="U24" s="7"/>
+      <c r="V24" s="7"/>
+      <c r="W24" s="7"/>
+      <c r="X24" s="7"/>
+      <c r="Y24" s="7"/>
+      <c r="Z24" s="7"/>
+      <c r="AA24" s="7"/>
+      <c r="AB24" s="2"/>
+    </row>
     <row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <row r="27" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5673,7 +5729,9 @@
     <row r="997" ht="15.75" customHeight="1"/>
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
+  <autoFilter ref="A1:AB24" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>

--- a/Ambiente Productivo/Lift-and-Shift - 18 Servers/analysis_TCO.xlsx
+++ b/Ambiente Productivo/Lift-and-Shift - 18 Servers/analysis_TCO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\C29652e\projects\Assessment\Assessment\Ambiente Productivo\Lift-and-Shift - 18 Servers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{640EC051-7138-40DA-BDB3-7171491C3AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{912172C8-B3CE-4AA2-85A5-3A8A1CEB78D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="127">
   <si>
     <t>Host Name Onpremise</t>
   </si>
@@ -4035,31 +4035,79 @@
       <c r="B13" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
+      <c r="C13" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="9">
+        <v>4</v>
+      </c>
+      <c r="E13" s="9">
+        <v>16</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13" s="9">
+        <v>2</v>
+      </c>
+      <c r="K13" s="9">
+        <v>16</v>
+      </c>
+      <c r="L13" s="9">
+        <v>240</v>
+      </c>
       <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="9"/>
+      <c r="N13" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="O13" s="9">
+        <v>9.6</v>
+      </c>
+      <c r="P13" s="9">
+        <f t="shared" ref="P13" si="4">PRODUCT(O13,12)</f>
+        <v>115.19999999999999</v>
+      </c>
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
-      <c r="S13" s="9"/>
-      <c r="T13" s="9"/>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
-      <c r="AA13" s="9"/>
+      <c r="S13" s="9">
+        <v>149.65</v>
+      </c>
+      <c r="T13" s="9">
+        <f t="shared" ref="T13" si="5">PRODUCT(S13,12)</f>
+        <v>1795.8000000000002</v>
+      </c>
+      <c r="U13" s="9">
+        <v>806</v>
+      </c>
+      <c r="V13" s="9">
+        <v>990</v>
+      </c>
+      <c r="W13" s="9">
+        <v>118.99</v>
+      </c>
+      <c r="X13" s="9">
+        <f t="shared" ref="X13" si="6">PRODUCT(W13,12)</f>
+        <v>1427.8799999999999</v>
+      </c>
+      <c r="Y13" s="9">
+        <v>622</v>
+      </c>
+      <c r="Z13" s="9">
+        <v>102.93</v>
+      </c>
+      <c r="AA13" s="9">
+        <f t="shared" ref="AA13" si="7">PRODUCT(Z13,12)</f>
+        <v>1235.1600000000001</v>
+      </c>
       <c r="AB13" s="2"/>
     </row>
     <row r="14" spans="1:28" s="13" customFormat="1" ht="15.75" customHeight="1">
@@ -5733,6 +5781,6 @@
   </sheetData>
   <autoFilter ref="A1:AB24" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>